--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484602_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484602_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9915</v>
+        <v>3.8079</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4216</v>
+        <v>3.0893</v>
       </c>
       <c r="F2" t="n">
-        <v>0.57</v>
+        <v>0.7186</v>
       </c>
       <c r="G2" t="n">
         <v>1.6398</v>
@@ -610,13 +610,13 @@
         <v>2.1991</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1971</v>
+        <v>0.0136</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4993</v>
+        <v>0.1671</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3021</v>
+        <v>-0.1535</v>
       </c>
       <c r="V2" t="n">
         <v>0.3219</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5721000000000001</v>
+        <v>0.5776</v>
       </c>
       <c r="E4" t="n">
-        <v>1.17</v>
+        <v>1.2251</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5979</v>
+        <v>-0.6475</v>
       </c>
       <c r="G4" t="n">
         <v>0.7145</v>
@@ -766,13 +766,13 @@
         <v>0.9163</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0587</v>
+        <v>-1.0532</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6056</v>
+        <v>-0.5505</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4531</v>
+        <v>-0.5027</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2999</v>
+        <v>-0.1047</v>
       </c>
       <c r="E5" t="n">
-        <v>2.0503</v>
+        <v>2.1465</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3502</v>
+        <v>-2.2511</v>
       </c>
       <c r="G5" t="n">
         <v>-0.0726</v>
@@ -844,13 +844,13 @@
         <v>0.3665</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5938</v>
+        <v>-0.3986</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2753</v>
+        <v>-0.1791</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3186</v>
+        <v>-0.2195</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3522</v>
+        <v>-0.1182</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6159</v>
+        <v>0.726</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9681</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="G6" t="n">
         <v>0.1776</v>
@@ -922,13 +922,13 @@
         <v>1.2828</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5298</v>
+        <v>-1.2958</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5324</v>
+        <v>-0.4223</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9974</v>
+        <v>-0.8735000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0.6335</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>A. VIVES HURTADO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9274</v>
+        <v>-2.1388</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.9885</v>
+        <v>-1.3549</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0611</v>
+        <v>-0.7839</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0674</v>
+        <v>-2.7252</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2825</v>
+        <v>-1.7409</v>
       </c>
       <c r="I7" t="n">
-        <v>0.215</v>
+        <v>-0.9843</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6409</v>
+        <v>-1.0887</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.728</v>
+        <v>-1.1303</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0871</v>
+        <v>0.0417</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5735</v>
+        <v>-1.6365</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4456</v>
+        <v>-0.6106</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1279</v>
+        <v>-1.0259</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.5498</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0158</v>
+        <v>-0.1833</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0158</v>
+        <v>0.733</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.538</v>
+        <v>0.0366</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3318</v>
+        <v>-0.083</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2062</v>
+        <v>0.1195</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.3219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. VIVES HURTADO</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5348</v>
+        <v>-2.3094</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6022</v>
+        <v>-4.2219</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9326</v>
+        <v>1.9125</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7252</v>
+        <v>-1.0674</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7409</v>
+        <v>-1.2825</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9843</v>
+        <v>0.215</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0887</v>
+        <v>-1.6409</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1303</v>
+        <v>-1.728</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0417</v>
+        <v>0.0871</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6365</v>
+        <v>0.5735</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6106</v>
+        <v>0.4456</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0259</v>
+        <v>0.1279</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5498</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="R8" t="n">
-        <v>0.733</v>
+        <v>2.0158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3594</v>
+        <v>-0.9201</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3303</v>
+        <v>-0.5652</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0291</v>
+        <v>-0.3549</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3219</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3199</v>
+        <v>-3.4474</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.7382</v>
+        <v>-3.1473</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4183</v>
+        <v>-0.3001</v>
       </c>
       <c r="G9" t="n">
         <v>-5.5263</v>
@@ -1156,13 +1156,13 @@
         <v>1.8326</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0001</v>
+        <v>-0.1276</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.23</v>
+        <v>-0.6391</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2299</v>
+        <v>0.5115</v>
       </c>
       <c r="V9" t="n">
         <v>3.4894</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. GUTIERREZ MARCO</t>
+          <t>G. GARCIA BURGOS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1839</v>
+        <v>-3.6507</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9996</v>
+        <v>-4.7263</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1844</v>
+        <v>1.0755</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.4264</v>
+        <v>-0.6012999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3908</v>
+        <v>0.011</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0356</v>
+        <v>-0.6124000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2779</v>
+        <v>-1.6312</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4029</v>
+        <v>-0.4742</v>
       </c>
       <c r="L10" t="n">
-        <v>0.125</v>
+        <v>-1.157</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1486</v>
+        <v>1.0299</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0121</v>
+        <v>0.4852</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1606</v>
+        <v>0.5446</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.1833</v>
+        <v>-2.0158</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.0158</v>
+        <v>-3.8484</v>
       </c>
       <c r="R10" t="n">
         <v>1.8326</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.3072</v>
+        <v>-1.667</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9728</v>
+        <v>-0.8356</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3344</v>
+        <v>-0.8315</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.267</v>
+        <v>0.6335</v>
       </c>
       <c r="W10" t="n">
-        <v>1.267</v>
+        <v>1.5889</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.5339</v>
+        <v>-0.9554</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>G. GARCIA BURGOS</t>
+          <t>A. GUTIERREZ MARCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3</v>
+        <v>-3.9751</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.0287</v>
+        <v>-2.6421</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7287</v>
+        <v>-1.333</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.6012999999999999</v>
+        <v>-1.4264</v>
       </c>
       <c r="H11" t="n">
-        <v>0.011</v>
+        <v>-1.3908</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.0356</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6312</v>
+        <v>-1.2779</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.4742</v>
+        <v>-1.4029</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.157</v>
+        <v>0.125</v>
       </c>
       <c r="M11" t="n">
-        <v>1.0299</v>
+        <v>-0.1486</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4852</v>
+        <v>0.0121</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5446</v>
+        <v>-0.1606</v>
       </c>
       <c r="P11" t="n">
+        <v>-0.1833</v>
+      </c>
+      <c r="Q11" t="n">
         <v>-2.0158</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>-3.8484</v>
       </c>
       <c r="R11" t="n">
         <v>1.8326</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.3163</v>
+        <v>-1.0984</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.138</v>
+        <v>-0.6153999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1783</v>
+        <v>-0.4831</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6335</v>
+        <v>-1.267</v>
       </c>
       <c r="W11" t="n">
-        <v>1.5889</v>
+        <v>1.267</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.9554</v>
+        <v>-2.5339</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9447</v>
+        <v>-5.403</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7007</v>
+        <v>-3.3572</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.244</v>
+        <v>-2.0458</v>
       </c>
       <c r="G12" t="n">
         <v>-5.8483</v>
@@ -1390,13 +1390,13 @@
         <v>1.2828</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9131</v>
+        <v>-0.3714</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5324</v>
+        <v>-0.1889</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3807</v>
+        <v>-0.1825</v>
       </c>
       <c r="V12" t="n">
         <v>0.6335</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0998</v>
+        <v>-5.8114</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.102</v>
+        <v>-2.8135</v>
       </c>
       <c r="F13" t="n">
         <v>-2.9978</v>
@@ -1468,10 +1468,10 @@
         <v>1.2828</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.733</v>
+        <v>-0.4446</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6976</v>
+        <v>-0.4091</v>
       </c>
       <c r="U13" t="n">
         <v>-0.0355</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-22.4488</v>
+        <v>-21.623</v>
       </c>
       <c r="E14" t="n">
-        <v>-14.9519</v>
+        <v>-14.1261</v>
       </c>
       <c r="F14" t="n">
         <v>-7.4969</v>
@@ -1513,7 +1513,7 @@
         <v>-15.914</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.8153</v>
+        <v>-5.815300000000001</v>
       </c>
       <c r="I14" t="n">
         <v>-10.0988</v>
@@ -1522,7 +1522,7 @@
         <v>-1.8901</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6094000000000004</v>
+        <v>-0.6093999999999995</v>
       </c>
       <c r="L14" t="n">
         <v>-1.2806</v>
@@ -1537,7 +1537,7 @@
         <v>-8.818199999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9161999999999997</v>
+        <v>-0.9162000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>-16.4931</v>
@@ -1546,19 +1546,19 @@
         <v>15.5769</v>
       </c>
       <c r="S14" t="n">
-        <v>-8.1523</v>
+        <v>-7.3265</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.1469</v>
+        <v>-4.321099999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.0055</v>
+        <v>-3.0057</v>
       </c>
       <c r="V14" t="n">
-        <v>2.534</v>
+        <v>2.534000000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>8.578000000000001</v>
+        <v>8.577999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-6.044</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.847300000000001</v>
+        <v>9.389200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>4.6682</v>
+        <v>5.0528</v>
       </c>
       <c r="F15" t="n">
-        <v>4.1792</v>
+        <v>4.3365</v>
       </c>
       <c r="G15" t="n">
         <v>5.8289</v>
@@ -1624,13 +1624,13 @@
         <v>2.0158</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3012</v>
+        <v>0.8431</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2949</v>
+        <v>0.0898</v>
       </c>
       <c r="U15" t="n">
-        <v>0.596</v>
+        <v>0.7534</v>
       </c>
       <c r="V15" t="n">
         <v>2.5339</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.4702</v>
+        <v>7.2502</v>
       </c>
       <c r="E16" t="n">
-        <v>7.4247</v>
+        <v>7.3286</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0455</v>
+        <v>-0.0784</v>
       </c>
       <c r="G16" t="n">
         <v>4.9322</v>
@@ -1702,13 +1702,13 @@
         <v>2.0158</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5222</v>
+        <v>0.3022</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1666</v>
+        <v>-0.2628</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6889</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.0761</v>
+        <v>3.3514</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2345</v>
+        <v>-0.0422</v>
       </c>
       <c r="F17" t="n">
-        <v>3.3106</v>
+        <v>3.3936</v>
       </c>
       <c r="G17" t="n">
         <v>2.2831</v>
@@ -1780,13 +1780,13 @@
         <v>2.5656</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1491</v>
+        <v>1.4244</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1991</v>
+        <v>0.3914</v>
       </c>
       <c r="U17" t="n">
-        <v>0.95</v>
+        <v>1.033</v>
       </c>
       <c r="V17" t="n">
         <v>0.0104</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.7141</v>
+        <v>1.9298</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1787</v>
+        <v>-0.1098</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5354</v>
+        <v>2.0396</v>
       </c>
       <c r="G18" t="n">
         <v>0.4033</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7323</v>
+        <v>0.948</v>
       </c>
       <c r="T18" t="n">
-        <v>0.6946</v>
+        <v>0.4061</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0377</v>
+        <v>0.5417999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0.945</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPIÑA</t>
+          <t>L. RODRIGUEZ CAMPINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2502</v>
+        <v>1.6871</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2502</v>
+        <v>-0.6209</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.308</v>
       </c>
       <c r="G19" t="n">
-        <v>1.2502</v>
+        <v>1.3051</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.378</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2502</v>
+        <v>2.6831</v>
       </c>
       <c r="J19" t="n">
-        <v>1.2502</v>
+        <v>0.8933</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>-1.3411</v>
       </c>
       <c r="L19" t="n">
-        <v>1.2502</v>
+        <v>2.2345</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>0.4118</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>-0.0368</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.4486</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.3665</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.3823</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1.2824</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>0.5014999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.7809</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>L. RODRIGUEZ CAMPINA</t>
+          <t>L. RODRIGUEZ CAMPIÑA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.1888</v>
+        <v>1.2502</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8133</v>
+        <v>1.2502</v>
       </c>
       <c r="F20" t="n">
-        <v>2.0021</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>1.3051</v>
+        <v>1.2502</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.378</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2.6831</v>
+        <v>1.2502</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8933</v>
+        <v>1.2502</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3411</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2345</v>
+        <v>1.2502</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4118</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0368</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4486</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3665</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3823</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7842</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3092</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4749</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.267</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.079</v>
+        <v>1.0542</v>
       </c>
       <c r="E21" t="n">
         <v>-0.7798</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8588</v>
+        <v>1.834</v>
       </c>
       <c r="G21" t="n">
         <v>0.2636</v>
@@ -2092,13 +2092,13 @@
         <v>1.6493</v>
       </c>
       <c r="S21" t="n">
-        <v>1.3206</v>
+        <v>1.2958</v>
       </c>
       <c r="T21" t="n">
         <v>0.6576</v>
       </c>
       <c r="U21" t="n">
-        <v>0.663</v>
+        <v>0.6382</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3219</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4383</v>
+        <v>0.5344</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7573</v>
+        <v>0.8535</v>
       </c>
       <c r="F22" t="n">
         <v>-0.319</v>
@@ -2170,10 +2170,10 @@
         <v>1.0995</v>
       </c>
       <c r="S22" t="n">
-        <v>0.7692</v>
+        <v>0.8653999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2368</v>
+        <v>0.333</v>
       </c>
       <c r="U22" t="n">
         <v>0.5324</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MELGAR GARCIA</t>
+          <t>H. FABREGAT LORES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.1172</v>
+        <v>-0.383</v>
       </c>
       <c r="E23" t="n">
-        <v>0.07389999999999999</v>
+        <v>-1.551</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.191</v>
+        <v>1.168</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5228</v>
+        <v>1.7189</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5866</v>
+        <v>-0.7494</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.9361</v>
+        <v>2.4683</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.6387</v>
+        <v>0.2782</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.44</v>
+        <v>-1.1645</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.1987</v>
+        <v>1.4427</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.884</v>
+        <v>1.4407</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1466</v>
+        <v>0.4151</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7374000000000001</v>
+        <v>1.0256</v>
       </c>
       <c r="P23" t="n">
-        <v>1.4661</v>
+        <v>-1.2828</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.0158</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4661</v>
+        <v>0.733</v>
       </c>
       <c r="S23" t="n">
-        <v>1.8845</v>
+        <v>0.7698</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3907</v>
+        <v>0.1867</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4939</v>
+        <v>0.5831</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.945</v>
+        <v>-1.5889</v>
       </c>
       <c r="W23" t="n">
-        <v>0.3219</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.267</v>
+        <v>-1.5889</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>H. FABREGAT LORES</t>
+          <t>A. MELGAR GARCIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5826</v>
+        <v>-0.6693</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6471</v>
+        <v>-0.503</v>
       </c>
       <c r="F24" t="n">
-        <v>1.0645</v>
+        <v>-0.1663</v>
       </c>
       <c r="G24" t="n">
-        <v>1.7189</v>
+        <v>-2.5228</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7494</v>
+        <v>-0.5866</v>
       </c>
       <c r="I24" t="n">
-        <v>2.4683</v>
+        <v>-1.9361</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2782</v>
+        <v>-1.6387</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1645</v>
+        <v>-0.44</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4427</v>
+        <v>-1.1987</v>
       </c>
       <c r="M24" t="n">
-        <v>1.4407</v>
+        <v>-0.884</v>
       </c>
       <c r="N24" t="n">
-        <v>0.4151</v>
+        <v>-0.1466</v>
       </c>
       <c r="O24" t="n">
-        <v>1.0256</v>
+        <v>-0.7374000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.2828</v>
+        <v>1.4661</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.0158</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.733</v>
+        <v>1.4661</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5702</v>
+        <v>1.3324</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0905</v>
+        <v>0.8137</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4797</v>
+        <v>0.5187</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.5889</v>
+        <v>-0.945</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.3219</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.5889</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.9155</v>
+        <v>-1.6635</v>
       </c>
       <c r="E25" t="n">
         <v>-3.3813</v>
       </c>
       <c r="F25" t="n">
-        <v>1.4658</v>
+        <v>1.7179</v>
       </c>
       <c r="G25" t="n">
         <v>-0.7673</v>
@@ -2404,13 +2404,13 @@
         <v>1.8326</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1188</v>
+        <v>0.3709</v>
       </c>
       <c r="T25" t="n">
         <v>-0.1116</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2304</v>
+        <v>0.4824</v>
       </c>
       <c r="V25" t="n">
         <v>-1.267</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>22.4487</v>
+        <v>23.7307</v>
       </c>
       <c r="E26" t="n">
-        <v>7.497000000000002</v>
+        <v>7.4971</v>
       </c>
       <c r="F26" t="n">
-        <v>14.9519</v>
+        <v>16.2339</v>
       </c>
       <c r="G26" t="n">
         <v>15.914</v>
@@ -2482,13 +2482,13 @@
         <v>16.493</v>
       </c>
       <c r="S26" t="n">
-        <v>8.1523</v>
+        <v>9.4344</v>
       </c>
       <c r="T26" t="n">
         <v>3.0054</v>
       </c>
       <c r="U26" t="n">
-        <v>5.1469</v>
+        <v>6.4289</v>
       </c>
       <c r="V26" t="n">
         <v>-2.534</v>
